--- a/db/ike_params_process_data.xlsx
+++ b/db/ike_params_process_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\local_repos\_private\ike_gui\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucag\local_repos\ike_gui\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF18CD1-7DA3-45B3-8C6A-08BF500796F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F14B140-5716-4A37-B6AB-FE785A8E0F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{35ECC9C5-EA02-4EE7-AAE2-09095EF705F3}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="fixed_point" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">process_data!$A$1:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">process_data!$A$1:$N$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="142">
   <si>
     <t>type</t>
   </si>
@@ -227,9 +227,6 @@
     <t>apertura scr</t>
   </si>
   <si>
-    <t>contatore isr timer 0</t>
-  </si>
-  <si>
     <t>frequenza attuale ingresso</t>
   </si>
   <si>
@@ -254,9 +251,6 @@
     <t>diagn_out.scr_synch_invalid_cnt</t>
   </si>
   <si>
-    <t>diagn_out.main_fsm_loop_time_ms</t>
-  </si>
-  <si>
     <t>tensione uscita (rms)</t>
   </si>
   <si>
@@ -449,13 +443,31 @@
     <t>valore massimo apertura scr</t>
   </si>
   <si>
-    <t>01.02.03</t>
-  </si>
-  <si>
     <t>V/u12</t>
   </si>
   <si>
     <t>A/u12</t>
+  </si>
+  <si>
+    <t>en protezione sovraccorrente AC</t>
+  </si>
+  <si>
+    <t>protection.en_prot_overcurr</t>
+  </si>
+  <si>
+    <t>diagn_out.main_fsm_update_isr_cnt_ms</t>
+  </si>
+  <si>
+    <t>contatore isr main_fsm_update</t>
+  </si>
+  <si>
+    <t>diagn_out.freq_in_update_isr_cnt_ms</t>
+  </si>
+  <si>
+    <t>contatore isr freq_in_update</t>
+  </si>
+  <si>
+    <t>01.02.05</t>
   </si>
 </sst>
 </file>
@@ -519,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -542,16 +554,13 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -563,7 +572,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -579,9 +588,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -619,7 +628,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -725,7 +734,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -867,7 +876,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -875,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041AAE19-AD56-4293-9964-80E5B30A6810}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -906,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>17</v>
@@ -933,16 +942,16 @@
         <v>1</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
@@ -978,7 +987,7 @@
         <v>23</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>59</v>
@@ -995,7 +1004,7 @@
         <f t="shared" ref="O2:O19" si="2">1/M2</f>
         <v>1</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="11">
         <f t="shared" ref="P2:P19" si="3">ROUND((F2-H2)*M2,0)</f>
         <v>0</v>
       </c>
@@ -1034,10 +1043,10 @@
         <v>23</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M3" s="7">
         <f t="shared" si="0"/>
@@ -1051,14 +1060,14 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P3" s="12">
+      <c r="P3" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A19" si="5">A3+1</f>
+        <f t="shared" ref="A4:A20" si="5">A3+1</f>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1093,7 +1102,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M4" s="7">
         <f t="shared" si="0"/>
@@ -1107,7 +1116,7 @@
         <f t="shared" si="2"/>
         <v>1.5259021896696422E-5</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="11">
         <f t="shared" si="3"/>
         <v>6554</v>
       </c>
@@ -1146,10 +1155,10 @@
         <v>30</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M5" s="7">
         <f>65535/(I5-H5)</f>
@@ -1163,7 +1172,7 @@
         <f>1/M5</f>
         <v>1.0681315327687494E-5</v>
       </c>
-      <c r="P5" s="12">
+      <c r="P5" s="11">
         <f>ROUND((F5-H5)*M5,0)</f>
         <v>60854</v>
       </c>
@@ -1205,7 +1214,7 @@
         <v>31</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M6" s="7">
         <f>65535/(I6-H6)</f>
@@ -1219,7 +1228,7 @@
         <f>1/M6</f>
         <v>1.5259021896696422E-5</v>
       </c>
-      <c r="P6" s="12">
+      <c r="P6" s="11">
         <f>ROUND((F6-H6)*M6,0)</f>
         <v>3277</v>
       </c>
@@ -1261,7 +1270,7 @@
         <v>32</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M7" s="7">
         <f>65535/(I7-H7)</f>
@@ -1275,7 +1284,7 @@
         <f>1/M7</f>
         <v>1.5259021896696422E-5</v>
       </c>
-      <c r="P7" s="12">
+      <c r="P7" s="11">
         <f>ROUND((F7-H7)*M7,0)</f>
         <v>3277</v>
       </c>
@@ -1311,13 +1320,13 @@
         <v>65535</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M8" s="7">
         <f>65535/(I8-H8)</f>
@@ -1331,7 +1340,7 @@
         <f>1/M8</f>
         <v>1</v>
       </c>
-      <c r="P8" s="12">
+      <c r="P8" s="11">
         <f>ROUND((F8-H8)*M8,0)</f>
         <v>2000</v>
       </c>
@@ -1367,13 +1376,13 @@
         <v>65535</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M9" s="7">
         <f t="shared" si="0"/>
@@ -1387,7 +1396,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P9" s="12">
+      <c r="P9" s="11">
         <f t="shared" si="3"/>
         <v>6000</v>
       </c>
@@ -1426,10 +1435,10 @@
         <v>23</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M10" s="7">
         <f t="shared" ref="M10" si="6">65535/(I10-H10)</f>
@@ -1443,7 +1452,7 @@
         <f t="shared" ref="O10" si="8">1/M10</f>
         <v>1</v>
       </c>
-      <c r="P10" s="12">
+      <c r="P10" s="11">
         <f t="shared" ref="P10" si="9">ROUND((F10-H10)*M10,0)</f>
         <v>0</v>
       </c>
@@ -1462,20 +1471,20 @@
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>0.1</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <f t="shared" si="4"/>
         <v>22000</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <v>22000</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <v>15000</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="15">
         <v>30000</v>
       </c>
       <c r="J11" s="5" t="s">
@@ -1485,7 +1494,7 @@
         <v>35</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M11" s="7">
         <f t="shared" si="0"/>
@@ -1499,7 +1508,7 @@
         <f t="shared" si="2"/>
         <v>0.22888532845044635</v>
       </c>
-      <c r="P11" s="12">
+      <c r="P11" s="11">
         <f t="shared" si="3"/>
         <v>30583</v>
       </c>
@@ -1518,20 +1527,20 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>0.1</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <f t="shared" si="4"/>
         <v>2000</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="15">
         <v>2000</v>
       </c>
-      <c r="H12" s="16">
-        <v>0</v>
-      </c>
-      <c r="I12" s="16">
+      <c r="H12" s="15">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
         <v>20000</v>
       </c>
       <c r="J12" s="5" t="s">
@@ -1541,7 +1550,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M12" s="7">
         <f t="shared" si="0"/>
@@ -1555,7 +1564,7 @@
         <f t="shared" si="2"/>
         <v>0.30518043793392846</v>
       </c>
-      <c r="P12" s="12">
+      <c r="P12" s="11">
         <f t="shared" si="3"/>
         <v>6554</v>
       </c>
@@ -1574,20 +1583,20 @@
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <v>0.1</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <v>2.5</v>
       </c>
-      <c r="H13" s="16">
-        <v>0</v>
-      </c>
-      <c r="I13" s="16">
+      <c r="H13" s="15">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
         <v>100</v>
       </c>
       <c r="J13" s="4" t="s">
@@ -1597,7 +1606,7 @@
         <v>37</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M13" s="7">
         <f t="shared" si="0"/>
@@ -1611,7 +1620,7 @@
         <f t="shared" si="2"/>
         <v>1.5259021896696422E-3</v>
       </c>
-      <c r="P13" s="12">
+      <c r="P13" s="11">
         <f t="shared" si="3"/>
         <v>1638</v>
       </c>
@@ -1647,13 +1656,13 @@
         <v>65535</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="M14" s="7">
         <f t="shared" ref="M14" si="10">65535/(I14-H14)</f>
@@ -1667,7 +1676,7 @@
         <f t="shared" ref="O14" si="12">1/M14</f>
         <v>1</v>
       </c>
-      <c r="P14" s="12">
+      <c r="P14" s="11">
         <f t="shared" ref="P14" si="13">ROUND((F14-H14)*M14,0)</f>
         <v>6000</v>
       </c>
@@ -1703,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>38</v>
@@ -1723,7 +1732,7 @@
         <f t="shared" si="2"/>
         <v>1.5259021896696422E-5</v>
       </c>
-      <c r="P15" s="12">
+      <c r="P15" s="11">
         <f t="shared" si="3"/>
         <v>5601</v>
       </c>
@@ -1779,7 +1788,7 @@
         <f t="shared" si="2"/>
         <v>3.0518043793392844E-3</v>
       </c>
-      <c r="P16" s="12">
+      <c r="P16" s="11">
         <f t="shared" si="3"/>
         <v>32768</v>
       </c>
@@ -1815,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>40</v>
@@ -1835,7 +1844,7 @@
         <f t="shared" si="2"/>
         <v>1.5259021896696422E-5</v>
       </c>
-      <c r="P17" s="12">
+      <c r="P17" s="11">
         <f t="shared" si="3"/>
         <v>320</v>
       </c>
@@ -1891,7 +1900,7 @@
         <f t="shared" si="2"/>
         <v>3.0518043793392844E-3</v>
       </c>
-      <c r="P18" s="12">
+      <c r="P18" s="11">
         <f t="shared" si="3"/>
         <v>32768</v>
       </c>
@@ -1947,9 +1956,65 @@
         <f t="shared" si="2"/>
         <v>1.5259021896696422E-4</v>
       </c>
-      <c r="P19" s="12">
+      <c r="P19" s="11">
         <f t="shared" si="3"/>
         <v>6554</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <f t="shared" ref="F20" si="14">G20</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>65535</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M20" s="7">
+        <f t="shared" ref="M20" si="15">65535/(I20-H20)</f>
+        <v>1</v>
+      </c>
+      <c r="N20" s="7">
+        <f t="shared" ref="N20" si="16">1/M20</f>
+        <v>1</v>
+      </c>
+      <c r="O20" s="7">
+        <f t="shared" ref="O20" si="17">1/M20</f>
+        <v>1</v>
+      </c>
+      <c r="P20" s="11">
+        <f t="shared" ref="P20" si="18">ROUND((F20-H20)*M20,0)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1960,7 +2025,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931DECF4-8BF0-4C1D-87E4-E5713582A1AF}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -1972,7 +2037,7 @@
     <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -1989,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>16</v>
@@ -2010,24 +2075,24 @@
         <v>1</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>MAX(params_data!A:A)+1</f>
-        <v>18</v>
-      </c>
-      <c r="B2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2049,13 +2114,13 @@
         <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="11" t="s">
         <v>58</v>
       </c>
       <c r="K2" s="7">
-        <f t="shared" ref="K2:K25" si="0">65535/(G2-F2)</f>
+        <f t="shared" ref="K2:K26" si="0">65535/(G2-F2)</f>
         <v>1</v>
       </c>
       <c r="L2" s="7">
@@ -2063,10 +2128,10 @@
         <v>1</v>
       </c>
       <c r="M2" s="7">
-        <f t="shared" ref="M2:M25" si="1">1/K2</f>
-        <v>1</v>
-      </c>
-      <c r="N2" s="15">
+        <f t="shared" ref="M2:M26" si="1">1/K2</f>
+        <v>1</v>
+      </c>
+      <c r="N2" s="14">
         <f>ROUND((E2-F2)*K2,0)</f>
         <v>0</v>
       </c>
@@ -2074,9 +2139,9 @@
     <row r="3" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>A2+1</f>
-        <v>19</v>
-      </c>
-      <c r="B3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2098,9 +2163,9 @@
         <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J3" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>57</v>
       </c>
       <c r="K3" s="7">
@@ -2108,24 +2173,24 @@
         <v>1</v>
       </c>
       <c r="L3" s="7">
-        <f t="shared" ref="L3:L25" si="2">1/K3</f>
+        <f t="shared" ref="L3:L26" si="2">1/K3</f>
         <v>1</v>
       </c>
       <c r="M3" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N3" s="15">
-        <f t="shared" ref="N3:N25" si="3">ROUND((E3-F3)*K3,0)</f>
+      <c r="N3" s="14">
+        <f t="shared" ref="N3:N26" si="3">ROUND((E3-F3)*K3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A25" si="4">A3+1</f>
-        <v>20</v>
-      </c>
-      <c r="B4" s="12" t="s">
+        <f t="shared" ref="A4:A26" si="4">A3+1</f>
+        <v>21</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2143,14 +2208,14 @@
       <c r="G4" s="3">
         <v>600</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>94</v>
+        <v>69</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>92</v>
       </c>
       <c r="K4" s="7">
         <f t="shared" si="0"/>
@@ -2164,7 +2229,7 @@
         <f t="shared" si="1"/>
         <v>9.1554131380178535E-3</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2172,9 +2237,9 @@
     <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-      <c r="B5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2192,14 +2257,14 @@
       <c r="G5" s="4">
         <v>50</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>28</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>95</v>
+        <v>70</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" si="0"/>
@@ -2213,7 +2278,7 @@
         <f t="shared" si="1"/>
         <v>7.6295109483482109E-4</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2221,9 +2286,9 @@
     <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="4"/>
-        <v>22</v>
-      </c>
-      <c r="B6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2241,14 +2306,14 @@
       <c r="G6" s="3">
         <v>600</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>96</v>
+        <v>71</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="K6" s="7">
         <f t="shared" si="0"/>
@@ -2262,7 +2327,7 @@
         <f t="shared" si="1"/>
         <v>9.1554131380178535E-3</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2270,12 +2335,12 @@
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="4"/>
-        <v>23</v>
-      </c>
-      <c r="B7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D7" s="1">
@@ -2290,14 +2355,14 @@
       <c r="G7" s="4">
         <v>50</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>97</v>
+      <c r="I7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="K7" s="7">
         <f t="shared" si="0"/>
@@ -2311,7 +2376,7 @@
         <f t="shared" si="1"/>
         <v>7.6295109483482109E-4</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2319,12 +2384,12 @@
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="4"/>
-        <v>24</v>
-      </c>
-      <c r="B8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D8" s="1">
@@ -2339,14 +2404,14 @@
       <c r="G8" s="3">
         <v>180</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>98</v>
+      <c r="I8" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
@@ -2360,7 +2425,7 @@
         <f t="shared" si="1"/>
         <v>3.0518043793392844E-3</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="14">
         <f t="shared" si="3"/>
         <v>6554</v>
       </c>
@@ -2368,12 +2433,12 @@
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="4"/>
-        <v>25</v>
-      </c>
-      <c r="B9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="1">
@@ -2388,14 +2453,14 @@
       <c r="G9" s="3">
         <v>180</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>99</v>
+      <c r="I9" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>97</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
@@ -2409,7 +2474,7 @@
         <f t="shared" si="1"/>
         <v>3.0518043793392844E-3</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="14">
         <f t="shared" si="3"/>
         <v>6554</v>
       </c>
@@ -2417,12 +2482,12 @@
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="B10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="1">
@@ -2437,14 +2502,14 @@
       <c r="G10" s="4">
         <v>100</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>100</v>
+      <c r="H10" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="K10" s="7">
         <f t="shared" si="0"/>
@@ -2458,7 +2523,7 @@
         <f t="shared" si="1"/>
         <v>1.5259021896696422E-3</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2466,34 +2531,34 @@
     <row r="11" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="4"/>
-        <v>27</v>
-      </c>
-      <c r="B11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="16">
-        <v>0</v>
-      </c>
-      <c r="F11" s="16">
-        <v>0</v>
-      </c>
-      <c r="G11" s="16">
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15">
         <v>50000</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>131</v>
+      <c r="I11" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="K11" s="7">
         <f t="shared" si="0"/>
@@ -2507,7 +2572,7 @@
         <f t="shared" si="1"/>
         <v>0.76295109483482115</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2515,12 +2580,12 @@
     <row r="12" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="4"/>
-        <v>28</v>
-      </c>
-      <c r="B12" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="1">
@@ -2535,14 +2600,14 @@
       <c r="G12" s="1">
         <v>65535</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>130</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="K12" s="7">
         <f t="shared" ref="K12" si="5">65535/(G12-F12)</f>
@@ -2556,7 +2621,7 @@
         <f t="shared" ref="M12" si="7">1/K12</f>
         <v>1</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="14">
         <f t="shared" ref="N12" si="8">ROUND((E12-F12)*K12,0)</f>
         <v>0</v>
       </c>
@@ -2564,12 +2629,12 @@
     <row r="13" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="4"/>
-        <v>29</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="1">
@@ -2584,41 +2649,41 @@
       <c r="G13" s="1">
         <v>65535</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>70</v>
+      <c r="H13" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="K13" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K13" si="9">65535/(G13-F13)</f>
         <v>1</v>
       </c>
       <c r="L13" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L13" si="10">1/K13</f>
         <v>1</v>
       </c>
       <c r="M13" s="7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N13" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="M13" si="11">1/K13</f>
+        <v>1</v>
+      </c>
+      <c r="N13" s="14">
+        <f t="shared" ref="N13" si="12">ROUND((E13-F13)*K13,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="4"/>
-        <v>30</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="1">
@@ -2633,41 +2698,41 @@
       <c r="G14" s="1">
         <v>65535</v>
       </c>
-      <c r="H14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>69</v>
+      <c r="H14" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>139</v>
       </c>
       <c r="K14" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K14" si="13">65535/(G14-F14)</f>
         <v>1</v>
       </c>
       <c r="L14" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L14" si="14">1/K14</f>
         <v>1</v>
       </c>
       <c r="M14" s="7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N14" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="M14" si="15">1/K14</f>
+        <v>1</v>
+      </c>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14" si="16">ROUND((E14-F14)*K14,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="4"/>
-        <v>31</v>
-      </c>
-      <c r="B15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="1">
@@ -2682,14 +2747,14 @@
       <c r="G15" s="1">
         <v>65535</v>
       </c>
-      <c r="H15" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>101</v>
+      <c r="H15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" si="0"/>
@@ -2703,7 +2768,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2711,12 +2776,12 @@
     <row r="16" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-      <c r="B16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="1">
@@ -2731,14 +2796,14 @@
       <c r="G16" s="1">
         <v>65535</v>
       </c>
-      <c r="H16" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>102</v>
+      <c r="H16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="K16" s="7">
         <f t="shared" si="0"/>
@@ -2752,7 +2817,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2760,12 +2825,12 @@
     <row r="17" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="4"/>
-        <v>33</v>
-      </c>
-      <c r="B17" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="1">
@@ -2780,14 +2845,14 @@
       <c r="G17" s="1">
         <v>65535</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>103</v>
+      <c r="H17" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="K17" s="7">
         <f t="shared" si="0"/>
@@ -2801,7 +2866,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2809,12 +2874,12 @@
     <row r="18" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="4"/>
-        <v>34</v>
-      </c>
-      <c r="B18" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="1">
@@ -2829,14 +2894,14 @@
       <c r="G18" s="1">
         <v>65535</v>
       </c>
-      <c r="H18" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>105</v>
+      <c r="H18" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="K18" s="7">
         <f t="shared" si="0"/>
@@ -2850,7 +2915,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2858,12 +2923,12 @@
     <row r="19" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="4"/>
-        <v>35</v>
-      </c>
-      <c r="B19" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="1">
@@ -2878,14 +2943,14 @@
       <c r="G19" s="1">
         <v>65535</v>
       </c>
-      <c r="H19" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>104</v>
+      <c r="H19" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="K19" s="7">
         <f t="shared" si="0"/>
@@ -2899,7 +2964,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2907,12 +2972,12 @@
     <row r="20" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="4"/>
-        <v>36</v>
-      </c>
-      <c r="B20" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="1">
@@ -2927,14 +2992,14 @@
       <c r="G20" s="1">
         <v>65535</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>106</v>
+      <c r="J20" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="K20" s="7">
         <f t="shared" si="0"/>
@@ -2948,7 +3013,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2956,12 +3021,12 @@
     <row r="21" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="B21" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="1">
@@ -2976,14 +3041,14 @@
       <c r="G21" s="1">
         <v>65535</v>
       </c>
-      <c r="H21" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>107</v>
+      <c r="H21" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="K21" s="7">
         <f t="shared" si="0"/>
@@ -2997,7 +3062,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N21" s="15">
+      <c r="N21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3005,12 +3070,12 @@
     <row r="22" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="4"/>
-        <v>38</v>
-      </c>
-      <c r="B22" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="1">
@@ -3025,14 +3090,14 @@
       <c r="G22" s="1">
         <v>65535</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>108</v>
+      <c r="H22" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>105</v>
       </c>
       <c r="K22" s="7">
         <f t="shared" si="0"/>
@@ -3046,7 +3111,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N22" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3054,12 +3119,12 @@
     <row r="23" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="4"/>
-        <v>39</v>
-      </c>
-      <c r="B23" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="1">
@@ -3077,129 +3142,178 @@
       <c r="H23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>111</v>
+      <c r="I23" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="K23" s="7">
-        <f t="shared" ref="K23" si="9">65535/(G23-F23)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L23" s="7">
-        <f t="shared" ref="L23" si="10">1/K23</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M23" s="7">
-        <f t="shared" ref="M23" si="11">1/K23</f>
-        <v>1</v>
-      </c>
-      <c r="N23" s="15">
-        <f t="shared" ref="N23" si="12">ROUND((E23-F23)*K23,0)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N23" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>50</v>
+        <v>41</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="D24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="J24" s="12" t="s">
-        <v>119</v>
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>65535</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="K24" s="7">
-        <f>65535/(G24-F24)</f>
-        <v>65535</v>
+        <f t="shared" ref="K24" si="17">65535/(G24-F24)</f>
+        <v>1</v>
       </c>
       <c r="L24" s="7">
-        <f>1/K24</f>
-        <v>1.5259021896696422E-5</v>
+        <f t="shared" ref="L24" si="18">1/K24</f>
+        <v>1</v>
       </c>
       <c r="M24" s="7">
-        <f>1/K24</f>
-        <v>1.5259021896696422E-5</v>
-      </c>
-      <c r="N24" s="15">
-        <f>ROUND((E24-F24)*K24,0)</f>
+        <f t="shared" ref="M24" si="19">1/K24</f>
+        <v>1</v>
+      </c>
+      <c r="N24" s="14">
+        <f t="shared" ref="N24" si="20">ROUND((E24-F24)*K24,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="4"/>
-        <v>41</v>
-      </c>
-      <c r="B25" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="K25" s="7">
+        <f>65535/(G25-F25)</f>
+        <v>65535</v>
+      </c>
+      <c r="L25" s="7">
+        <f>1/K25</f>
+        <v>1.5259021896696422E-5</v>
+      </c>
+      <c r="M25" s="7">
+        <f>1/K25</f>
+        <v>1.5259021896696422E-5</v>
+      </c>
+      <c r="N25" s="14">
+        <f>ROUND((E25-F25)*K25,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="4"/>
+        <v>43</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="1">
         <v>3</v>
       </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3">
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>65</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H26" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="K25" s="7">
+      <c r="I26" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="K26" s="7">
         <f t="shared" si="0"/>
         <v>1008.2307692307693</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L26" s="7">
         <f t="shared" si="2"/>
         <v>9.9183642328526736E-4</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M26" s="7">
         <f t="shared" si="1"/>
         <v>9.9183642328526736E-4</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N26" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N25" xr:uid="{931DECF4-8BF0-4C1D-87E4-E5713582A1AF}"/>
+  <autoFilter ref="A1:N26" xr:uid="{931DECF4-8BF0-4C1D-87E4-E5713582A1AF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3211,8 +3325,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>135</v>
+      <c r="A1" s="11" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3244,16 +3358,16 @@
       <c r="B1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>48</v>
       </c>
       <c r="G1" s="8"/>
@@ -3270,23 +3384,23 @@
       <c r="B2" s="8">
         <v>0</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <f t="shared" ref="C2:C10" si="0">POWER(2,B2)</f>
         <v>1</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <f t="shared" ref="D2:D10" si="1">ROUND((POWER(2,A2)-H2), B2)</f>
         <v>65535</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f t="shared" ref="E2:E10" si="2">ROUND((-D2/2),B2)</f>
         <v>-32768</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <f t="shared" ref="F2:F10" si="3">ROUND((D2/2-H2),B2)</f>
         <v>32767</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <f t="shared" ref="G2:G10" si="4">ROUND(D2*POWER(2,B2),0)</f>
         <v>65535</v>
       </c>
@@ -3304,23 +3418,23 @@
       <c r="B3" s="8">
         <v>1</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <f t="shared" si="1"/>
         <v>32767.5</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <f t="shared" si="2"/>
         <v>-16383.8</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <f t="shared" si="3"/>
         <v>16383.3</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <f t="shared" si="4"/>
         <v>65535</v>
       </c>
@@ -3338,23 +3452,23 @@
       <c r="B4" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <f t="shared" si="1"/>
         <v>16383.75</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <f t="shared" si="2"/>
         <v>-8191.88</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <f t="shared" si="3"/>
         <v>8191.63</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <f t="shared" si="4"/>
         <v>65535</v>
       </c>
@@ -3372,23 +3486,23 @@
       <c r="B5" s="8">
         <v>3</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f t="shared" si="1"/>
         <v>8191.875</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <f t="shared" si="2"/>
         <v>-4095.9380000000001</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <f t="shared" si="3"/>
         <v>4095.8130000000001</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <f t="shared" si="4"/>
         <v>65535</v>
       </c>
@@ -3406,23 +3520,23 @@
       <c r="B6" s="8">
         <v>4</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f t="shared" si="1"/>
         <v>4095.9375</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <f t="shared" si="2"/>
         <v>-2047.9688000000001</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <f t="shared" si="3"/>
         <v>2047.9063000000001</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <f t="shared" si="4"/>
         <v>65535</v>
       </c>
@@ -3440,23 +3554,23 @@
       <c r="B7" s="8">
         <v>5</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f t="shared" si="1"/>
         <v>2047.96875</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <f t="shared" si="2"/>
         <v>-1023.98438</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <f t="shared" si="3"/>
         <v>1023.95313</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <f t="shared" si="4"/>
         <v>65535</v>
       </c>
@@ -3474,23 +3588,23 @@
       <c r="B8" s="8">
         <v>6</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f t="shared" si="1"/>
         <v>1023.984375</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <f t="shared" si="2"/>
         <v>-511.992188</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <f t="shared" si="3"/>
         <v>511.976563</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <f t="shared" si="4"/>
         <v>65535</v>
       </c>
@@ -3502,33 +3616,33 @@
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>9</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>7</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f t="shared" si="1"/>
         <v>511.9921875</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <f t="shared" si="2"/>
         <v>-255.99609380000001</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <f t="shared" si="3"/>
         <v>255.98828130000001</v>
       </c>
-      <c r="G9" s="11">
-        <f t="shared" si="4"/>
-        <v>65535</v>
-      </c>
-      <c r="H9" s="9">
+      <c r="G9" s="10">
+        <f t="shared" si="4"/>
+        <v>65535</v>
+      </c>
+      <c r="H9" s="8">
         <f t="shared" si="5"/>
         <v>7.8125E-3</v>
       </c>
@@ -3536,33 +3650,33 @@
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>8</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <f t="shared" si="0"/>
         <v>256</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f t="shared" si="1"/>
         <v>255.99609375</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <f t="shared" si="2"/>
         <v>-127.99804688</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <f t="shared" si="3"/>
         <v>127.99414063</v>
       </c>
-      <c r="G10" s="11">
-        <f t="shared" si="4"/>
-        <v>65535</v>
-      </c>
-      <c r="H10" s="9">
+      <c r="G10" s="10">
+        <f t="shared" si="4"/>
+        <v>65535</v>
+      </c>
+      <c r="H10" s="8">
         <f t="shared" si="5"/>
         <v>3.90625E-3</v>
       </c>
@@ -3570,7 +3684,7 @@
       <c r="M10" s="4"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E15" s="14"/>
+      <c r="E15" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/db/ike_params_process_data.xlsx
+++ b/db/ike_params_process_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucag\local_repos\ike_gui\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F14B140-5716-4A37-B6AB-FE785A8E0F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145C36BA-318D-425C-9A48-9C61151E7076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{35ECC9C5-EA02-4EE7-AAE2-09095EF705F3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{35ECC9C5-EA02-4EE7-AAE2-09095EF705F3}"/>
   </bookViews>
   <sheets>
     <sheet name="params_data" sheetId="9" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="fixed_point" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">process_data!$A$1:$N$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">process_data!$A$1:$N$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -248,9 +248,6 @@
     <t>word allarme 1</t>
   </si>
   <si>
-    <t>diagn_out.scr_synch_invalid_cnt</t>
-  </si>
-  <si>
     <t>tensione uscita (rms)</t>
   </si>
   <si>
@@ -467,7 +464,10 @@
     <t>contatore isr freq_in_update</t>
   </si>
   <si>
-    <t>01.02.05</t>
+    <t>scr_out.scr_synch_invalid_cnt</t>
+  </si>
+  <si>
+    <t>01.02.06</t>
   </si>
 </sst>
 </file>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>17</v>
@@ -942,16 +942,16 @@
         <v>1</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
@@ -1043,10 +1043,10 @@
         <v>23</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M3" s="7">
         <f t="shared" si="0"/>
@@ -1102,7 +1102,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M4" s="7">
         <f t="shared" si="0"/>
@@ -1130,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -1155,10 +1155,10 @@
         <v>30</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M5" s="7">
         <f>65535/(I5-H5)</f>
@@ -1214,7 +1214,7 @@
         <v>31</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M6" s="7">
         <f>65535/(I6-H6)</f>
@@ -1270,7 +1270,7 @@
         <v>32</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M7" s="7">
         <f>65535/(I7-H7)</f>
@@ -1320,13 +1320,13 @@
         <v>65535</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M8" s="7">
         <f>65535/(I8-H8)</f>
@@ -1376,13 +1376,13 @@
         <v>65535</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M9" s="7">
         <f t="shared" si="0"/>
@@ -1435,10 +1435,10 @@
         <v>23</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="M10" s="7">
         <f t="shared" ref="M10" si="6">65535/(I10-H10)</f>
@@ -1494,7 +1494,7 @@
         <v>35</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M11" s="7">
         <f t="shared" si="0"/>
@@ -1550,7 +1550,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M12" s="7">
         <f t="shared" si="0"/>
@@ -1606,7 +1606,7 @@
         <v>37</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M13" s="7">
         <f t="shared" si="0"/>
@@ -1656,13 +1656,13 @@
         <v>65535</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="M14" s="7">
         <f t="shared" ref="M14" si="10">65535/(I14-H14)</f>
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>38</v>
@@ -1824,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>40</v>
@@ -1995,10 +1995,10 @@
         <v>23</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="M20" s="7">
         <f t="shared" ref="M20" si="15">65535/(I20-H20)</f>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>16</v>
@@ -2075,16 +2075,16 @@
         <v>1</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="N1" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -2120,7 +2120,7 @@
         <v>58</v>
       </c>
       <c r="K2" s="7">
-        <f t="shared" ref="K2:K26" si="0">65535/(G2-F2)</f>
+        <f t="shared" ref="K2:K25" si="0">65535/(G2-F2)</f>
         <v>1</v>
       </c>
       <c r="L2" s="7">
@@ -2128,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="7">
-        <f t="shared" ref="M2:M26" si="1">1/K2</f>
+        <f t="shared" ref="M2:M25" si="1">1/K2</f>
         <v>1</v>
       </c>
       <c r="N2" s="14">
@@ -2173,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="7">
-        <f t="shared" ref="L3:L26" si="2">1/K3</f>
+        <f t="shared" ref="L3:L25" si="2">1/K3</f>
         <v>1</v>
       </c>
       <c r="M3" s="7">
@@ -2181,7 +2181,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="14">
-        <f t="shared" ref="N3:N26" si="3">ROUND((E3-F3)*K3,0)</f>
+        <f t="shared" ref="N3:N25" si="3">ROUND((E3-F3)*K3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2212,10 +2212,10 @@
         <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K4" s="7">
         <f t="shared" si="0"/>
@@ -2261,10 +2261,10 @@
         <v>28</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" si="0"/>
@@ -2310,10 +2310,10 @@
         <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K6" s="7">
         <f t="shared" si="0"/>
@@ -2359,10 +2359,10 @@
         <v>28</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K7" s="7">
         <f t="shared" si="0"/>
@@ -2411,7 +2411,7 @@
         <v>63</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
@@ -2460,7 +2460,7 @@
         <v>64</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
@@ -2503,13 +2503,13 @@
         <v>100</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>62</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K10" s="7">
         <f t="shared" si="0"/>
@@ -2555,10 +2555,10 @@
         <v>26</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K11" s="7">
         <f t="shared" si="0"/>
@@ -2601,13 +2601,13 @@
         <v>65535</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I12" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>128</v>
       </c>
       <c r="K12" s="7">
         <f t="shared" ref="K12" si="5">65535/(G12-F12)</f>
@@ -2650,13 +2650,13 @@
         <v>65535</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K13" s="7">
         <f t="shared" ref="K13" si="9">65535/(G13-F13)</f>
@@ -2699,13 +2699,13 @@
         <v>65535</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K14" s="7">
         <f t="shared" ref="K14" si="13">65535/(G14-F14)</f>
@@ -2748,13 +2748,13 @@
         <v>65535</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" si="0"/>
@@ -2895,13 +2895,13 @@
         <v>65535</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>85</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K18" s="7">
         <f t="shared" si="0"/>
@@ -2944,13 +2944,13 @@
         <v>65535</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K19" s="7">
         <f t="shared" si="0"/>
@@ -2993,13 +2993,13 @@
         <v>65535</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K20" s="7">
         <f t="shared" si="0"/>
@@ -3090,11 +3090,11 @@
       <c r="G22" s="1">
         <v>65535</v>
       </c>
-      <c r="H22" s="12" t="s">
-        <v>81</v>
+      <c r="H22" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>105</v>
@@ -3143,25 +3143,25 @@
         <v>23</v>
       </c>
       <c r="I23" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J23" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J23" s="11" t="s">
-        <v>106</v>
-      </c>
       <c r="K23" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K23" si="17">65535/(G23-F23)</f>
         <v>1</v>
       </c>
       <c r="L23" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L23" si="18">1/K23</f>
         <v>1</v>
       </c>
       <c r="M23" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M23" si="19">1/K23</f>
         <v>1</v>
       </c>
       <c r="N23" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="N23" si="20">ROUND((E23-F23)*K23,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -3171,46 +3171,46 @@
         <v>41</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>65535</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>23</v>
+        <v>2</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K24" s="7">
-        <f t="shared" ref="K24" si="17">65535/(G24-F24)</f>
-        <v>1</v>
+        <f>65535/(G24-F24)</f>
+        <v>65535</v>
       </c>
       <c r="L24" s="7">
-        <f t="shared" ref="L24" si="18">1/K24</f>
-        <v>1</v>
+        <f>1/K24</f>
+        <v>1.5259021896696422E-5</v>
       </c>
       <c r="M24" s="7">
-        <f t="shared" ref="M24" si="19">1/K24</f>
-        <v>1</v>
+        <f>1/K24</f>
+        <v>1.5259021896696422E-5</v>
       </c>
       <c r="N24" s="14">
-        <f t="shared" ref="N24" si="20">ROUND((E24-F24)*K24,0)</f>
+        <f>ROUND((E24-F24)*K24,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
         <v>50</v>
       </c>
       <c r="D25" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
@@ -3235,31 +3235,31 @@
         <v>0</v>
       </c>
       <c r="G25" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K25" s="7">
-        <f>65535/(G25-F25)</f>
-        <v>65535</v>
+        <f t="shared" si="0"/>
+        <v>1008.2307692307693</v>
       </c>
       <c r="L25" s="7">
-        <f>1/K25</f>
-        <v>1.5259021896696422E-5</v>
+        <f t="shared" si="2"/>
+        <v>9.9183642328526736E-4</v>
       </c>
       <c r="M25" s="7">
-        <f>1/K25</f>
-        <v>1.5259021896696422E-5</v>
+        <f t="shared" si="1"/>
+        <v>9.9183642328526736E-4</v>
       </c>
       <c r="N25" s="14">
-        <f>ROUND((E25-F25)*K25,0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3272,48 +3272,48 @@
         <v>53</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D26" s="1">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
-        <v>65</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>65535</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="K26" s="7">
-        <f t="shared" si="0"/>
-        <v>1008.2307692307693</v>
+        <f t="shared" ref="K26" si="21">65535/(G26-F26)</f>
+        <v>1</v>
       </c>
       <c r="L26" s="7">
-        <f t="shared" si="2"/>
-        <v>9.9183642328526736E-4</v>
+        <f t="shared" ref="L26" si="22">1/K26</f>
+        <v>1</v>
       </c>
       <c r="M26" s="7">
-        <f t="shared" si="1"/>
-        <v>9.9183642328526736E-4</v>
+        <f t="shared" ref="M26" si="23">1/K26</f>
+        <v>1</v>
       </c>
       <c r="N26" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="N26" si="24">ROUND((E26-F26)*K26,0)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N26" xr:uid="{931DECF4-8BF0-4C1D-87E4-E5713582A1AF}"/>
+  <autoFilter ref="A1:N25" xr:uid="{931DECF4-8BF0-4C1D-87E4-E5713582A1AF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
